--- a/input/newQuestion.xlsx
+++ b/input/newQuestion.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\c++\projects\QuestionGenerator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B445BD87-3A0C-4660-9A79-11FF5020E466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6996AE60-6852-486D-A26E-5E7CD6C2062B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Question No</t>
   </si>
@@ -43,9 +48,71 @@
     <t>answer</t>
   </si>
   <si>
+    <t>what is 5 percent of 100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">what is 23 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>percent of 84 into 100</t>
+    </r>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>What is 23 percent of 84 multiplied by 100, assuming that the calculation is performed in the most standard arithmetic manner, where you first convert the percentage into its decimal form, apply it to the number 84, and then take the resulting value and multiply it by 100?</t>
   </si>
   <si>
+    <t>The value obtained by first calculating 23% of 84 and then multiplying the outcome by 100, resulting in 1932, which is the final expanded numerical value after both operations.</t>
+  </si>
+  <si>
+    <t>) A number slightly above two thousand but still below three thousand, because the process of multiplying by 100 significantly increases the earlier computed percentage value.</t>
+  </si>
+  <si>
+    <t>A value less than one thousand because multiplying a percentage-based result generally reduces the overall magnitude instead of increasing it dramatically.</t>
+  </si>
+  <si>
+    <t>None of the above options correctly represent the final numeric result produced by performing the stated sequence of operations.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The value obtained by first calculating </t>
   </si>
   <si>
@@ -56,9 +123,6 @@
   </si>
   <si>
     <t>None of the above option</t>
-  </si>
-  <si>
-    <t>D</t>
   </si>
 </sst>
 </file>
@@ -76,7 +140,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -87,27 +154,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -116,15 +168,13 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -147,44 +197,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -211,14 +261,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -245,6 +296,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -256,194 +308,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="74.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -452,25 +485,415 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>134</v>
+      </c>
+      <c r="F3">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C5" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>134</v>
+      </c>
+      <c r="F5">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>134</v>
+      </c>
+      <c r="F7">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+      <c r="E9">
+        <v>134</v>
+      </c>
+      <c r="F9">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
         <v>12</v>
       </c>
+      <c r="E12">
+        <v>134</v>
+      </c>
+      <c r="F12">
+        <v>43</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>12</v>
+      </c>
+      <c r="E18">
+        <v>134</v>
+      </c>
+      <c r="F18">
+        <v>43</v>
+      </c>
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>12</v>
+      </c>
+      <c r="E19">
+        <v>134</v>
+      </c>
+      <c r="F19">
+        <v>43</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>